--- a/tulemused/koondtabel_pohjalik.xlsx
+++ b/tulemused/koondtabel_pohjalik.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karle\PycharmProjects\loputoo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karle\PycharmProjects\loputoo\tulemused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13852FAB-01DB-4743-BD1F-91771D83F183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF544B58-6BCE-4058-8353-C52403E814C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Hinded" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="461">
   <si>
     <t>Õpilane</t>
   </si>
@@ -1373,19 +1374,49 @@
     <t>AI kasutus üle 50%:</t>
   </si>
   <si>
-    <t>GPT-5.2</t>
-  </si>
-  <si>
-    <t>Gemini 3.1 Pro</t>
-  </si>
-  <si>
-    <t>GPT-5.1</t>
-  </si>
-  <si>
-    <t>Sonnet 4.5</t>
-  </si>
-  <si>
     <t>Keskmine TI %</t>
+  </si>
+  <si>
+    <t>GPT-5.2 - TI tõenäosus</t>
+  </si>
+  <si>
+    <t>GPT-5.1 - TI tõenäosus</t>
+  </si>
+  <si>
+    <t>Gemini 3.1 Pro - TI tõenäosus</t>
+  </si>
+  <si>
+    <t>Sonnet 4.5 - TI tõenäosus</t>
+  </si>
+  <si>
+    <t>AI kasutus % 0-10:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 20-30:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 10-20:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 30-40:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 40-50:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 50-60:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 60-70:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 80-90:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 90-100:</t>
+  </si>
+  <si>
+    <t>AI kasutus % 70-80:</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1501,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>GPT-5.2</c:v>
+                  <c:v>GPT-5.2 - TI tõenäosus</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1595,7 +1626,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>GPT-5.1</c:v>
+                  <c:v>GPT-5.1 - TI tõenäosus</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1720,7 +1751,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Gemini 3.1 Pro</c:v>
+                  <c:v>Gemini 3.1 Pro - TI tõenäosus</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1847,7 +1878,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Sonnet 4.5</c:v>
+                  <c:v>Sonnet 4.5 - TI tõenäosus</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2251,7 +2282,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$C$1</c15:sqref>
@@ -2314,7 +2345,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2372,7 +2403,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -2385,7 +2416,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$E$1</c15:sqref>
@@ -2448,7 +2479,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2509,7 +2540,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -2522,7 +2553,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$F$1</c15:sqref>
@@ -2585,7 +2616,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2643,7 +2674,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -2656,7 +2687,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$H$1</c15:sqref>
@@ -2721,7 +2752,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2782,7 +2813,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -2795,7 +2826,7 @@
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$I$1</c15:sqref>
@@ -2860,7 +2891,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2918,7 +2949,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -2931,7 +2962,7 @@
                 <c:order val="9"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$K$1</c15:sqref>
@@ -2996,7 +3027,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3057,7 +3088,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000009-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -3070,7 +3101,7 @@
                 <c:order val="10"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$L$1</c15:sqref>
@@ -3135,7 +3166,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3193,7 +3224,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000A-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -3206,7 +3237,7 @@
                 <c:order val="12"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Hinded!$N$1</c15:sqref>
@@ -3272,7 +3303,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -3330,7 +3361,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000C-8D06-4DCD-AF6A-7D912D8911D3}"/>
                   </c:ext>
@@ -4099,16 +4130,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>141</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>960120</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4421,27 +4452,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O141"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O151"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="50" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4452,7 +4483,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -4470,7 +4501,7 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
@@ -4479,16 +4510,16 @@
         <v>8</v>
       </c>
       <c r="M1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N1" t="s">
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>3084201</v>
       </c>
@@ -4535,7 +4566,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3084202</v>
       </c>
@@ -4582,7 +4613,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3084203</v>
       </c>
@@ -4629,7 +4660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3084207</v>
       </c>
@@ -4676,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3084208</v>
       </c>
@@ -4723,7 +4754,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3084209</v>
       </c>
@@ -4770,7 +4801,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3084211</v>
       </c>
@@ -4817,7 +4848,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3084212</v>
       </c>
@@ -4864,7 +4895,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3084213</v>
       </c>
@@ -4911,7 +4942,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3084214</v>
       </c>
@@ -4958,7 +4989,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3084215</v>
       </c>
@@ -5005,7 +5036,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3084217</v>
       </c>
@@ -5052,7 +5083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3084219</v>
       </c>
@@ -5099,7 +5130,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3084220</v>
       </c>
@@ -5146,7 +5177,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3084221</v>
       </c>
@@ -5193,7 +5224,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3084222</v>
       </c>
@@ -5240,7 +5271,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3084224</v>
       </c>
@@ -5287,7 +5318,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3084225</v>
       </c>
@@ -5334,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3084226</v>
       </c>
@@ -5381,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3084227</v>
       </c>
@@ -5428,7 +5459,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3084228</v>
       </c>
@@ -5475,7 +5506,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3084229</v>
       </c>
@@ -5522,7 +5553,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3084230</v>
       </c>
@@ -5569,7 +5600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3084232</v>
       </c>
@@ -5616,7 +5647,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>3084234</v>
       </c>
@@ -5663,7 +5694,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3084235</v>
       </c>
@@ -5710,7 +5741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3084236</v>
       </c>
@@ -5757,7 +5788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3084237</v>
       </c>
@@ -5804,7 +5835,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3084238</v>
       </c>
@@ -5851,7 +5882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3084239</v>
       </c>
@@ -5898,7 +5929,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3084240</v>
       </c>
@@ -5945,7 +5976,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>3084242</v>
       </c>
@@ -5992,7 +6023,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3084244</v>
       </c>
@@ -6039,7 +6070,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3084245</v>
       </c>
@@ -6086,7 +6117,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3084246</v>
       </c>
@@ -6133,7 +6164,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3084248</v>
       </c>
@@ -6180,7 +6211,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3084249</v>
       </c>
@@ -6227,7 +6258,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3084250</v>
       </c>
@@ -6274,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3084252</v>
       </c>
@@ -6321,7 +6352,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>3084254</v>
       </c>
@@ -6368,7 +6399,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>3084256</v>
       </c>
@@ -6415,7 +6446,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3084257</v>
       </c>
@@ -6462,7 +6493,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3084258</v>
       </c>
@@ -6509,7 +6540,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3084260</v>
       </c>
@@ -6556,7 +6587,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>3084261</v>
       </c>
@@ -6603,7 +6634,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>3084263</v>
       </c>
@@ -6650,7 +6681,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>3084265</v>
       </c>
@@ -6697,7 +6728,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3084266</v>
       </c>
@@ -6744,7 +6775,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>3084269</v>
       </c>
@@ -6791,7 +6822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>3084270</v>
       </c>
@@ -6838,7 +6869,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3084271</v>
       </c>
@@ -6885,7 +6916,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>3084272</v>
       </c>
@@ -6932,7 +6963,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>3084274</v>
       </c>
@@ -6979,7 +7010,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>3084275</v>
       </c>
@@ -7026,7 +7057,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>3084277</v>
       </c>
@@ -7073,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>3084278</v>
       </c>
@@ -7120,7 +7151,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3084279</v>
       </c>
@@ -7167,7 +7198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>3084280</v>
       </c>
@@ -7214,7 +7245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>3084282</v>
       </c>
@@ -7261,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3084283</v>
       </c>
@@ -7308,7 +7339,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>3084285</v>
       </c>
@@ -7355,7 +7386,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>3084287</v>
       </c>
@@ -7402,7 +7433,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3084292</v>
       </c>
@@ -7449,7 +7480,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>3084294</v>
       </c>
@@ -7496,7 +7527,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>3084296</v>
       </c>
@@ -7543,7 +7574,7 @@
         <v>73.8</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3084297</v>
       </c>
@@ -7590,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>3084298</v>
       </c>
@@ -7637,7 +7668,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>3084299</v>
       </c>
@@ -7684,7 +7715,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3084300</v>
       </c>
@@ -7731,7 +7762,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3084301</v>
       </c>
@@ -7778,7 +7809,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>3084304</v>
       </c>
@@ -7825,7 +7856,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>3084308</v>
       </c>
@@ -7872,7 +7903,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>3084309</v>
       </c>
@@ -7919,7 +7950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>3084311</v>
       </c>
@@ -7966,7 +7997,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3084313</v>
       </c>
@@ -8013,7 +8044,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>3084314</v>
       </c>
@@ -8060,7 +8091,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>3084315</v>
       </c>
@@ -8107,7 +8138,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>3084316</v>
       </c>
@@ -8154,7 +8185,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>3084317</v>
       </c>
@@ -8201,7 +8232,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>3084318</v>
       </c>
@@ -8248,7 +8279,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>3084320</v>
       </c>
@@ -8295,7 +8326,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>3084321</v>
       </c>
@@ -8342,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>3084322</v>
       </c>
@@ -8389,7 +8420,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>3084324</v>
       </c>
@@ -8436,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>3084325</v>
       </c>
@@ -8483,7 +8514,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>3084327</v>
       </c>
@@ -8530,7 +8561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3084328</v>
       </c>
@@ -8577,7 +8608,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>3084329</v>
       </c>
@@ -8624,7 +8655,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>3084330</v>
       </c>
@@ -8671,7 +8702,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>3084332</v>
       </c>
@@ -8718,7 +8749,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>3084333</v>
       </c>
@@ -8765,7 +8796,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>3084334</v>
       </c>
@@ -8812,7 +8843,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>3084336</v>
       </c>
@@ -8859,7 +8890,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>3084337</v>
       </c>
@@ -8906,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>3084338</v>
       </c>
@@ -8953,7 +8984,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>3084339</v>
       </c>
@@ -9000,7 +9031,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>3084340</v>
       </c>
@@ -9047,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>3084342</v>
       </c>
@@ -9094,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>3084345</v>
       </c>
@@ -9141,7 +9172,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>3084346</v>
       </c>
@@ -9188,7 +9219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>3084348</v>
       </c>
@@ -9235,7 +9266,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>3084352</v>
       </c>
@@ -9282,7 +9313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>3084353</v>
       </c>
@@ -9329,7 +9360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>3084355</v>
       </c>
@@ -9376,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>3084356</v>
       </c>
@@ -9423,7 +9454,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>3084359</v>
       </c>
@@ -9470,7 +9501,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>3084361</v>
       </c>
@@ -9517,7 +9548,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>3084362</v>
       </c>
@@ -9564,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>3084364</v>
       </c>
@@ -9611,7 +9642,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>3084365</v>
       </c>
@@ -9658,7 +9689,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>3084366</v>
       </c>
@@ -9705,7 +9736,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>3084371</v>
       </c>
@@ -9752,7 +9783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>3084373</v>
       </c>
@@ -9799,7 +9830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>3084374</v>
       </c>
@@ -9846,7 +9877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>3084375</v>
       </c>
@@ -9893,7 +9924,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>3084377</v>
       </c>
@@ -9940,7 +9971,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>3084378</v>
       </c>
@@ -9987,7 +10018,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>3084381</v>
       </c>
@@ -10034,7 +10065,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>3084382</v>
       </c>
@@ -10081,7 +10112,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>3084383</v>
       </c>
@@ -10128,7 +10159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>3084384</v>
       </c>
@@ -10175,7 +10206,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>3084385</v>
       </c>
@@ -10222,7 +10253,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>3084388</v>
       </c>
@@ -10269,7 +10300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>3084389</v>
       </c>
@@ -10316,7 +10347,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>3084393</v>
       </c>
@@ -10363,7 +10394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>3084394</v>
       </c>
@@ -10410,7 +10441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>3084398</v>
       </c>
@@ -10457,7 +10488,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>3084400</v>
       </c>
@@ -10504,7 +10535,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>3084401</v>
       </c>
@@ -10551,7 +10582,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>3084402</v>
       </c>
@@ -10598,7 +10629,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>3084403</v>
       </c>
@@ -10645,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>3084404</v>
       </c>
@@ -10692,7 +10723,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>3084405</v>
       </c>
@@ -10739,7 +10770,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>3084407</v>
       </c>
@@ -10786,7 +10817,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>3084408</v>
       </c>
@@ -10833,7 +10864,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>3084409</v>
       </c>
@@ -10880,7 +10911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>444</v>
       </c>
@@ -10901,7 +10932,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>442</v>
       </c>
@@ -10922,7 +10953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>443</v>
       </c>
@@ -10963,7 +10994,7 @@
         <v>36.08</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>445</v>
       </c>
@@ -10986,6 +11017,216 @@
       <c r="O141">
         <f>COUNTIF(O2:O137, "&gt;50")</f>
         <v>37</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>451</v>
+      </c>
+      <c r="D142">
+        <f>COUNTIF(D2:D137, "&lt;=10")</f>
+        <v>23</v>
+      </c>
+      <c r="G142">
+        <f>COUNTIF(G2:G137, "&lt;=10")</f>
+        <v>23</v>
+      </c>
+      <c r="J142">
+        <f>COUNTIF(J2:J137, "&lt;=10")</f>
+        <v>109</v>
+      </c>
+      <c r="M142">
+        <f>COUNTIF(M2:M137, "&lt;=10")</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>453</v>
+      </c>
+      <c r="D143">
+        <f>COUNTIFS(D2:D137, "&gt;10", D2:D137, "&lt;=20")</f>
+        <v>2</v>
+      </c>
+      <c r="G143">
+        <f>COUNTIFS(G2:G137, "&gt;10", G2:G137, "&lt;=20")</f>
+        <v>5</v>
+      </c>
+      <c r="J143">
+        <f>COUNTIFS(J2:J137, "&gt;10", J2:J137, "&lt;=20")</f>
+        <v>17</v>
+      </c>
+      <c r="M143">
+        <f>COUNTIFS(M2:M137, "&gt;10", M2:M137, "&lt;=20")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>452</v>
+      </c>
+      <c r="D144">
+        <f>COUNTIFS(D2:D137, "&gt;20", D2:D137, "&lt;=30")</f>
+        <v>4</v>
+      </c>
+      <c r="G144">
+        <f>COUNTIFS(G2:G137, "&gt;20", G2:G137, "&lt;=30")</f>
+        <v>13</v>
+      </c>
+      <c r="J144">
+        <f>COUNTIFS(J2:J137, "&gt;20", J2:J137, "&lt;=30")</f>
+        <v>3</v>
+      </c>
+      <c r="M144">
+        <f>COUNTIFS(M2:M137, "&gt;20", M2:M137, "&lt;=30")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>454</v>
+      </c>
+      <c r="D145">
+        <f>COUNTIFS(D2:D137, "&gt;30", D2:D137, "&lt;=40")</f>
+        <v>11</v>
+      </c>
+      <c r="G145">
+        <f>COUNTIFS(G2:G137, "&gt;30", G2:G137, "&lt;=40")</f>
+        <v>32</v>
+      </c>
+      <c r="J145">
+        <f>COUNTIFS(J2:J137, "&gt;30", J2:J137, "&lt;=40")</f>
+        <v>2</v>
+      </c>
+      <c r="M145">
+        <f>COUNTIFS(M2:M137, "&gt;30", M2:M137, "&lt;=40")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>455</v>
+      </c>
+      <c r="D146">
+        <f>COUNTIFS(D2:D137, "&gt;40", D2:D137, "&lt;=50")</f>
+        <v>13</v>
+      </c>
+      <c r="G146">
+        <f>COUNTIFS(G2:G137, "&gt;40", G2:G137, "&lt;=50")</f>
+        <v>30</v>
+      </c>
+      <c r="J146">
+        <f>COUNTIFS(J2:J137, "&gt;40", J2:J137, "&lt;=50")</f>
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <f>COUNTIFS(M2:M137, "&gt;40", M2:M137, "&lt;=50")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>456</v>
+      </c>
+      <c r="D147">
+        <f>COUNTIFS(D2:D137, "&gt;50", D2:D137, "&lt;=60")</f>
+        <v>26</v>
+      </c>
+      <c r="G147">
+        <f>COUNTIFS(G2:G137, "&gt;50", G2:G137, "&lt;=60")</f>
+        <v>20</v>
+      </c>
+      <c r="J147">
+        <f>COUNTIFS(J2:J137, "&gt;50", J2:J137, "&lt;=60")</f>
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <f>COUNTIFS(M2:M137, "&gt;50", M2:M137, "&lt;=60")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>457</v>
+      </c>
+      <c r="D148">
+        <f>COUNTIFS(D2:D137, "&gt;60", D2:D137, "&lt;=70")</f>
+        <v>25</v>
+      </c>
+      <c r="G148">
+        <f>COUNTIFS(G2:G137, "&gt;60", G2:G137, "&lt;=70")</f>
+        <v>8</v>
+      </c>
+      <c r="J148">
+        <f>COUNTIFS(J2:J137, "&gt;60", J2:J137, "&lt;=70")</f>
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <f>COUNTIFS(M2:M137, "&gt;60", M2:M137, "&lt;=70")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>460</v>
+      </c>
+      <c r="D149">
+        <f>COUNTIFS(D2:D137, "&gt;70", D2:D137, "&lt;=80")</f>
+        <v>21</v>
+      </c>
+      <c r="G149">
+        <f>COUNTIFS(G2:G137, "&gt;70", G2:G137, "&lt;=80")</f>
+        <v>5</v>
+      </c>
+      <c r="J149">
+        <f>COUNTIFS(J2:J137, "&gt;70", J2:J137, "&lt;=80")</f>
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <f>COUNTIFS(M2:M137, "&gt;70", M2:M137, "&lt;=80")</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>458</v>
+      </c>
+      <c r="D150">
+        <f>COUNTIFS(D2:D137, "&gt;80", D2:D137, "&lt;=90")</f>
+        <v>10</v>
+      </c>
+      <c r="G150">
+        <f>COUNTIFS(G2:G137, "&gt;80", G2:G137, "&lt;=90")</f>
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <f>COUNTIFS(J2:J137, "&gt;80", J2:J137, "&lt;=90")</f>
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <f>COUNTIFS(M2:M137, "&gt;80", M2:M137, "&lt;=90")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>459</v>
+      </c>
+      <c r="D151">
+        <f>COUNTIFS(D2:D137, "&gt;90", D2:D137, "&lt;=100")</f>
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <f>COUNTIFS(G2:G137, "&gt;90", G2:G137, "&lt;=100")</f>
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <f>COUNTIFS(J2:J137, "&gt;90", J2:J137, "&lt;=100")</f>
+        <v>2</v>
+      </c>
+      <c r="M151">
+        <f>COUNTIFS(M2:M137, "&gt;90", M2:M137, "&lt;=100")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
